--- a/brain/library/internal/scorecards/Premium Pest Management Scorecard April 2026.xlsx
+++ b/brain/library/internal/scorecards/Premium Pest Management Scorecard April 2026.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +51,50 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001F3864"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -71,8 +113,26 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F3864"/>
+        <bgColor rgb="001F3864"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+        <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D6E4F0"/>
+        <bgColor rgb="00D6E4F0"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -80,11 +140,23 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="medium"/>
+      <bottom style="medium"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -97,6 +169,49 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -466,166 +581,166 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>INITIAL SCREEN: Premium Pest Management for Luxury Hospitality &amp; Food Service</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>Date: April 2026 | All 4 criteria must PASS to proceed to Industry Scorecard</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Criterion</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Finding</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Result</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>Margins</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="11" t="inlineStr">
         <is>
           <t>15%+ EBITDA</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="11" t="inlineStr">
         <is>
           <t>25-35% EBITDA for well-run operators</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D5" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Recurring Revenue</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Existing or convertible</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>70-85% recurring from monthly/quarterly service contracts</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D6" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>Industry Growth</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="11" t="inlineStr">
         <is>
           <t>Above GDP (~3%+)</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>5-6% CAGR; commercial pest control grew 9% in 2024</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D7" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Growth TAM</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>$500M+ market size</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>$26B US market (2025)</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D8" s="12" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="14" t="inlineStr">
         <is>
           <t>Target TAM (informational)</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>~21,800 independently owned firms. 37,000 food processing plants + ~1M restaurants.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="14" t="inlineStr">
         <is>
           <t>QSBS Eligibility</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Likely Eligible — not an enumerated excluded field. Value in routes/contracts, not individual skill.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>Sprint Duration</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Long sprint (21,800 targets). JJ cold calling at 10-20/day for months.</t>
         </is>
@@ -658,781 +773,781 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>INDUSTRY SCORECARD: Premium Pest Management for Luxury Hospitality &amp; Food Service</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>Scoring: + = 3, +/- = 2, - = 1 | Weighted average = FINAL SCORE</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Weight</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Sub-Criterion</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Score</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Reasoning</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Growth &amp; Catalyst</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>25%</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>Growth vs GDP</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="18" t="inlineStr">
         <is>
           <t>+/-</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E5" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="17" t="inlineStr">
         <is>
           <t>5-6% CAGR vs ~3% GDP = ~2x, solid not explosive</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr"/>
+      <c r="B6" s="19" t="inlineStr"/>
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>Penetration catalyst</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="D6" s="19" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="13" t="inlineStr">
         <is>
           <t>FDA/FSMA enforcement expanding, third-party audit proliferation</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr">
+      <c r="A7" s="11" t="inlineStr"/>
+      <c r="B7" s="20" t="inlineStr"/>
+      <c r="C7" s="11" t="inlineStr">
         <is>
           <t>Future growth</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" s="11" t="inlineStr">
         <is>
           <t>Climate, regulation, hospitality rebound — all tailwinds</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr"/>
+      <c r="B8" s="19" t="inlineStr"/>
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>Evidence</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="13" t="inlineStr">
         <is>
           <t>NPMA: 8% industry growth 2024, 9% commercial</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Size &amp; Fragmentation</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Number of players</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="D9" s="18" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="17" t="inlineStr">
         <is>
           <t>19,000+ firms, massive fragmentation</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr">
+      <c r="A10" s="13" t="inlineStr"/>
+      <c r="B10" s="19" t="inlineStr"/>
+      <c r="C10" s="13" t="inlineStr">
         <is>
           <t>Concentration</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="13" t="inlineStr">
         <is>
           <t>No firm controls &gt;15% market share</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="17" t="inlineStr">
         <is>
           <t>Industry Economics</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Gross margins</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="D11" s="18" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="17" t="inlineStr">
         <is>
           <t>60-70% gross margins</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr">
+      <c r="A12" s="13" t="inlineStr"/>
+      <c r="B12" s="19" t="inlineStr"/>
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>EBITDA margins</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="13" t="inlineStr">
         <is>
           <t>25-35% EBITDA</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr">
+      <c r="A13" s="11" t="inlineStr"/>
+      <c r="B13" s="20" t="inlineStr"/>
+      <c r="C13" s="11" t="inlineStr">
         <is>
           <t>ROTC</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" t="inlineStr">
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="11" t="inlineStr">
         <is>
           <t>Asset-light, high cash conversion, minimal CapEx</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Mission Criticality</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Value proposition clarity</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F14" s="17" t="inlineStr">
         <is>
           <t>Pest = urgent, visible problem. Non-discretionary.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr">
+      <c r="A15" s="11" t="inlineStr"/>
+      <c r="B15" s="20" t="inlineStr"/>
+      <c r="C15" s="11" t="inlineStr">
         <is>
           <t>Customer switching costs</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>3</v>
-      </c>
-      <c r="F15" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F15" s="11" t="inlineStr">
         <is>
           <t>HACCP documentation trail, audit cycle alignment</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
+      <c r="A16" s="13" t="inlineStr"/>
+      <c r="B16" s="19" t="inlineStr"/>
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>Feedback quality</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D16" s="19" t="inlineStr">
         <is>
           <t>+/-</t>
         </is>
       </c>
-      <c r="E16" t="n">
+      <c r="E16" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="13" t="inlineStr">
         <is>
           <t>Standard commercial: moderate. Food safety: high.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Exogenous Risks</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>Tech risk</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="18" t="inlineStr">
         <is>
           <t>+/-</t>
         </is>
       </c>
-      <c r="E17" s="6" t="n">
+      <c r="E17" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="17" t="inlineStr">
         <is>
           <t>IoT emerging but enhances, does not replace</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr">
+      <c r="A18" s="13" t="inlineStr"/>
+      <c r="B18" s="19" t="inlineStr"/>
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>Regulatory risk</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" t="inlineStr">
+      <c r="D18" s="19" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E18" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="13" t="inlineStr">
         <is>
           <t>Regulation is a TAILWIND — more regulation = more demand</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr">
+      <c r="A19" s="11" t="inlineStr"/>
+      <c r="B19" s="20" t="inlineStr"/>
+      <c r="C19" s="11" t="inlineStr">
         <is>
           <t>Liability</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>+/-</t>
         </is>
       </c>
-      <c r="E19" t="n">
+      <c r="E19" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="11" t="inlineStr">
         <is>
           <t>Chemical handling, some litigation risk</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr"/>
+      <c r="B20" s="19" t="inlineStr"/>
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Cyclicality</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>3</v>
-      </c>
-      <c r="F20" t="inlineStr">
+      <c r="D20" s="19" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E20" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>Non-discretionary, recession-resistant</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>Porter's Forces</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>15%</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="17" t="inlineStr">
         <is>
           <t>Competition</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="18" t="inlineStr">
         <is>
           <t>+/-</t>
         </is>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="18" t="n">
         <v>2</v>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="17" t="inlineStr">
         <is>
           <t>PE roll-ups active but market vast (19,000+ firms)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr">
+      <c r="A22" s="13" t="inlineStr"/>
+      <c r="B22" s="19" t="inlineStr"/>
+      <c r="C22" s="13" t="inlineStr">
         <is>
           <t>New entrants</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D22" s="19" t="inlineStr">
         <is>
           <t>+/-</t>
         </is>
       </c>
-      <c r="E22" t="n">
+      <c r="E22" s="19" t="n">
         <v>2</v>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="13" t="inlineStr">
         <is>
           <t>Moderate barrier (state licensing required)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
+      <c r="A23" s="11" t="inlineStr"/>
+      <c r="B23" s="20" t="inlineStr"/>
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>Supplier power</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>3</v>
-      </c>
-      <c r="F23" t="inlineStr">
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F23" s="11" t="inlineStr">
         <is>
           <t>Chemicals are commodity inputs</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr">
+      <c r="A24" s="13" t="inlineStr"/>
+      <c r="B24" s="19" t="inlineStr"/>
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>Customer power</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>3</v>
-      </c>
-      <c r="F24" t="inlineStr">
+      <c r="D24" s="19" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F24" s="13" t="inlineStr">
         <is>
           <t>Customers cannot opt out of pest control</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr"/>
+      <c r="B25" s="20" t="inlineStr"/>
+      <c r="C25" s="11" t="inlineStr">
         <is>
           <t>Substitutes</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
         <is>
           <t>No substitutes exist</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" s="17" t="inlineStr">
         <is>
           <t>Value Creation</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>10%</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="17" t="inlineStr">
         <is>
           <t>Professionalization</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E26" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F26" s="17" t="inlineStr">
         <is>
           <t>Tech-enable: digital monitoring, automated reporting</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr"/>
+      <c r="B27" s="20" t="inlineStr"/>
+      <c r="C27" s="11" t="inlineStr">
         <is>
           <t>Complexity</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D27" s="20" t="inlineStr">
         <is>
           <t>+/-</t>
         </is>
       </c>
-      <c r="E27" t="n">
+      <c r="E27" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="11" t="inlineStr">
         <is>
           <t>Moderate — not simple but learnable domain</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Impact</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr">
         <is>
           <t>5%</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="17" t="inlineStr">
         <is>
           <t>Net impact</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
-        <is>
-          <t>+</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>+</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="F28" s="17" t="inlineStr">
         <is>
           <t>Public health, food safety, disease prevention</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>WEIGHTED SCORE SUMMARY</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" s="10" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>Avg Score</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>Weighted</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="22" t="inlineStr">
         <is>
           <t>Growth &amp; Catalyst (25%)</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" s="23" t="n">
         <v>2.75</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C33" s="23" t="n">
         <v>0.6875</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="24" t="inlineStr">
         <is>
           <t>Size &amp; Fragmentation (10%)</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>3</v>
-      </c>
-      <c r="C34" t="n">
+      <c r="B34" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" s="25" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="22" t="inlineStr">
         <is>
           <t>Industry Economics (10%)</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>3</v>
-      </c>
-      <c r="C35" t="n">
+      <c r="B35" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="C35" s="23" t="n">
         <v>0.3</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="24" t="inlineStr">
         <is>
           <t>Mission Criticality (15%)</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="B36" s="25" t="n">
         <v>2.67</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C36" s="25" t="n">
         <v>0.4</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>Exogenous Risks (10%)</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="B37" s="23" t="n">
         <v>2.5</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C37" s="23" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="24" t="inlineStr">
         <is>
           <t>Porter's Forces (15%)</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B38" s="25" t="n">
         <v>2.6</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C38" s="25" t="n">
         <v>0.39</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="22" t="inlineStr">
         <is>
           <t>Value Creation (10%)</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="B39" s="23" t="n">
         <v>2.5</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C39" s="23" t="n">
         <v>0.25</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="24" t="inlineStr">
         <is>
           <t>Impact (5%)</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>3</v>
-      </c>
-      <c r="C40" t="n">
+      <c r="B40" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="C40" s="25" t="n">
         <v>0.15</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="inlineStr">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>TOTAL SCORE</t>
         </is>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="26" t="n">
         <v>2.73</v>
       </c>
-      <c r="C42" s="1" t="inlineStr">
+      <c r="C42" s="26" t="inlineStr">
         <is>
           <t>/ 3.0 (91%)</t>
         </is>
